--- a/Tabla_Grafico_Cascada_MORTALIDAD.xlsx
+++ b/Tabla_Grafico_Cascada_MORTALIDAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Downloads\TABLERO_STREAMLIT_DASHBOARD\DASHBOARD_Morbilidad_DESPLIEGUE_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4BC4AC8-0086-4091-85A2-73D9CEE9C7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9329A84C-7D2E-4E39-9FFD-63DCD171F87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{0D616C1C-8E0C-4C20-B986-F38AF72ECD6B}"/>
   </bookViews>
@@ -42,6 +42,30 @@
     <t>Arauca</t>
   </si>
   <si>
+    <t>Consum.Sust.Psicoact.</t>
+  </si>
+  <si>
+    <t>Esquizofrenia</t>
+  </si>
+  <si>
+    <t>Retr. Mental</t>
+  </si>
+  <si>
+    <t>Síndr. Alterac. Fisiológ.Fact.Físicos</t>
+  </si>
+  <si>
+    <t>Trast. Afect Estad.Animo</t>
+  </si>
+  <si>
+    <t>Trast.Person.Comp.Adultos</t>
+  </si>
+  <si>
+    <t>Trast. Desarrollo Psico.</t>
+  </si>
+  <si>
+    <t>Trast.Ment.Orgán. Sintomát.  </t>
+  </si>
+  <si>
     <t>Casanare</t>
   </si>
   <si>
@@ -51,37 +75,13 @@
     <t>Vichada</t>
   </si>
   <si>
+    <t>Trast.Habit. Niñez-Adolesc</t>
+  </si>
+  <si>
+    <t>Trast. Neurót. Estrés y Somatom.</t>
+  </si>
+  <si>
     <t>Tot_Eventos</t>
-  </si>
-  <si>
-    <t>Consumo de sustancias psicoactivas</t>
-  </si>
-  <si>
-    <t>Esquizofrenia Trastornos esquizotípicos y delirantes</t>
-  </si>
-  <si>
-    <t>Retraso mental</t>
-  </si>
-  <si>
-    <t>Síndromes del comportamiento  asociados a alteraciones fisiológicas y factores físicos</t>
-  </si>
-  <si>
-    <t>Trastornos (afectivos) del estado de ánimo</t>
-  </si>
-  <si>
-    <t>Trastornos de la personalidad y comportamiento en adultos</t>
-  </si>
-  <si>
-    <t>Trastornos del desarrollo psicológico</t>
-  </si>
-  <si>
-    <t>Trastornos habituales en la niñez y en la adolescencia</t>
-  </si>
-  <si>
-    <t>Trastornos mentales orgánicos, incluidos los sintomáticos,  </t>
-  </si>
-  <si>
-    <t>Trastornos neuróticos, trastornos relacionados con el estrés y somatomorfos</t>
   </si>
   <si>
     <t>Tasa_Mortalidad</t>
@@ -562,7 +562,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.109375" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="72.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -574,7 +574,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
@@ -587,8 +587,8 @@
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>8</v>
+      <c r="B2" t="s">
+        <v>4</v>
       </c>
       <c r="C2" s="5">
         <v>14562</v>
@@ -604,8 +604,8 @@
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
       <c r="C3" s="5">
         <v>19704</v>
@@ -621,8 +621,8 @@
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>10</v>
+      <c r="B4" t="s">
+        <v>6</v>
       </c>
       <c r="C4" s="5">
         <v>11340</v>
@@ -638,8 +638,8 @@
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>11</v>
+      <c r="B5" t="s">
+        <v>7</v>
       </c>
       <c r="C5" s="5">
         <v>10757</v>
@@ -655,8 +655,8 @@
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
+      <c r="B6" t="s">
+        <v>8</v>
       </c>
       <c r="C6" s="5">
         <v>56399</v>
@@ -672,8 +672,8 @@
       <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>13</v>
+      <c r="B7" t="s">
+        <v>9</v>
       </c>
       <c r="C7" s="5">
         <v>5682</v>
@@ -689,8 +689,8 @@
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>14</v>
+      <c r="B8" t="s">
+        <v>10</v>
       </c>
       <c r="C8" s="5">
         <v>46452</v>
@@ -706,7 +706,7 @@
       <c r="A9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="5">
@@ -723,8 +723,8 @@
       <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>16</v>
+      <c r="B10" t="s">
+        <v>11</v>
       </c>
       <c r="C10" s="5">
         <v>15545</v>
@@ -740,8 +740,8 @@
       <c r="A11" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>17</v>
+      <c r="B11" t="s">
+        <v>16</v>
       </c>
       <c r="C11" s="5">
         <v>83705</v>
@@ -755,10 +755,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
         <v>4</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
       </c>
       <c r="C12" s="5">
         <v>9066</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
       </c>
       <c r="C13" s="5">
         <v>17933</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
       </c>
       <c r="C14" s="5">
         <v>17615</v>
@@ -806,10 +806,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
       </c>
       <c r="C15" s="5">
         <v>10884</v>
@@ -823,10 +823,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="5" t="s">
         <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
       </c>
       <c r="C16" s="5">
         <v>83562</v>
@@ -840,10 +840,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
       </c>
       <c r="C17" s="5">
         <v>4037</v>
@@ -857,10 +857,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
       </c>
       <c r="C18" s="5">
         <v>60720</v>
@@ -874,9 +874,9 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="5">
@@ -891,10 +891,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
       </c>
       <c r="C20" s="5">
         <v>15528</v>
@@ -908,10 +908,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
       </c>
       <c r="C21" s="5">
         <v>102468</v>
@@ -925,10 +925,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
       </c>
       <c r="C22" s="5">
         <v>53432</v>
@@ -942,10 +942,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
         <v>5</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>9</v>
       </c>
       <c r="C23" s="5">
         <v>89356</v>
@@ -959,10 +959,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
       </c>
       <c r="C24" s="5">
         <v>72902</v>
@@ -976,10 +976,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
       </c>
       <c r="C25" s="5">
         <v>40615</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
       </c>
       <c r="C26" s="5">
         <v>223155</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="5" t="s">
         <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
       </c>
       <c r="C27" s="5">
         <v>19710</v>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
       </c>
       <c r="C28" s="5">
         <v>154268</v>
@@ -1044,9 +1044,9 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="5">
@@ -1061,10 +1061,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
       </c>
       <c r="C30" s="5">
         <v>79959</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
       </c>
       <c r="C31" s="5">
         <v>351299</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4</v>
       </c>
       <c r="C32" s="5">
         <v>1038</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>9</v>
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
       </c>
       <c r="C33" s="5">
         <v>2106</v>
@@ -1129,10 +1129,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" t="s">
         <v>6</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="C34" s="5">
         <v>1392</v>
@@ -1146,10 +1146,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
       </c>
       <c r="C35" s="5">
         <v>1188</v>
@@ -1163,10 +1163,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
       </c>
       <c r="C36" s="5">
         <v>4764</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="B37" t="s">
+        <v>9</v>
       </c>
       <c r="C37" s="5">
         <v>971</v>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="5" t="s">
         <v>14</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
       </c>
       <c r="C38" s="5">
         <v>1727</v>
@@ -1214,9 +1214,9 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="5">
@@ -1231,10 +1231,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
       </c>
       <c r="C40" s="5">
         <v>869</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
       </c>
       <c r="C41" s="9">
         <v>10386</v>
